--- a/output/pdf_financials_xlsx/AUXX.xlsx
+++ b/output/pdf_financials_xlsx/AUXX.xlsx
@@ -1080,22 +1080,22 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.440706</v>
+        <v>-0.440706</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>3.736792</v>
+        <v>-3.736792</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>3.014239</v>
+        <v>-3.014239</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.07467799999999999</v>
+        <v>-0.07467799999999999</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.059672</v>
+        <v>-0.059672</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.207794</v>
+        <v>-0.207794</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>6.649472</v>
@@ -1146,7 +1146,7 @@
         <v>-6.826</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-0</v>
+        <v>-1.50114</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>-0.277</v>
@@ -1304,28 +1304,28 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.440706</v>
+        <v>-0.440706</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>3.736792</v>
+        <v>-3.736792</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>3.014239</v>
+        <v>-3.014239</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.07467799999999999</v>
+        <v>-0.07467799999999999</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.059672</v>
+        <v>-0.059672</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.207794</v>
+        <v>-0.207794</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>13.475472</v>
+        <v>-13.475472</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.75057</v>
+        <v>-0.75057</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>-5.98033</v>
@@ -1439,28 +1439,28 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.440706</v>
+        <v>-0.440706</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>3.736792</v>
+        <v>-3.736792</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>3.014239</v>
+        <v>-3.014239</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.07467799999999999</v>
+        <v>-0.07467799999999999</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.059672</v>
+        <v>-0.059672</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.207794</v>
+        <v>-0.207794</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>13.475472</v>
+        <v>-13.475472</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.75057</v>
+        <v>-0.75057</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>-5.98033</v>
@@ -1578,13 +1578,13 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>11.01765</v>
+        <v>-11.01765</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>26.691371</v>
+        <v>-26.691371</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>27.402173</v>
+        <v>-27.402173</v>
       </c>
       <c r="F26" s="1" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>-5.19485</v>
+        <v>5.19485</v>
       </c>
       <c r="I26" s="1" t="inlineStr">
         <is>
@@ -1631,22 +1631,22 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.440706</v>
+        <v>-0.440706</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>3.736792</v>
+        <v>-3.736792</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>3.014239</v>
+        <v>-3.014239</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.07467799999999999</v>
+        <v>-0.07467799999999999</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.059672</v>
+        <v>-0.059672</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.207794</v>
+        <v>-0.207794</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>6.649472</v>
@@ -1721,22 +1721,22 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.440706</v>
+        <v>-0.440706</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>3.736792</v>
+        <v>-3.736792</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>3.014239</v>
+        <v>-3.014239</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.07467799999999999</v>
+        <v>-0.07467799999999999</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.059672</v>
+        <v>-0.059672</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.207794</v>
+        <v>-0.207794</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>6.649472</v>
@@ -1833,28 +1833,28 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>102.654767175499</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K31" s="3" t="n">
         <v>10.01613791462562</v>
@@ -4555,16 +4555,16 @@
         <v>1.203271</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>1.203271</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>7.373377</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>7.373377</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>7.295667</v>
       </c>
     </row>
     <row r="93">
@@ -5735,10 +5735,10 @@
         <v>0</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>0.279</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>0.998243</v>
       </c>
       <c r="F118" s="3" t="n">
         <v>0</v>
@@ -8270,7 +8270,11 @@
           <t>Reserve (Note 13) 7,384,771</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
@@ -9790,7 +9794,11 @@
           <t>Reserve (Note 13)</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>-</t>
@@ -10820,7 +10828,11 @@
           <t>Reserve (Note 4) 1,505,727</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
           <t>-</t>
@@ -24148,7 +24160,11 @@
           <t>Shares issued for exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D230" t="inlineStr"/>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E230" t="inlineStr">
         <is>
           <t>-</t>
@@ -24222,7 +24238,11 @@
           <t>Depreciation included in exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D231" t="inlineStr"/>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E231" t="inlineStr">
         <is>
           <t>-</t>
@@ -27189,13 +27209,13 @@
         </is>
       </c>
       <c r="N270" s="5" t="n">
-        <v>3.042537</v>
+        <v>-3.042537</v>
       </c>
       <c r="O270" s="5" t="n">
-        <v>10.264338</v>
+        <v>-10.264338</v>
       </c>
       <c r="P270" s="5" t="n">
-        <v>26.353535</v>
+        <v>-26.353535</v>
       </c>
     </row>
     <row r="271">
@@ -31747,10 +31767,10 @@
         </is>
       </c>
       <c r="L331" s="5" t="n">
-        <v>13.475472</v>
+        <v>-13.475472</v>
       </c>
       <c r="M331" s="5" t="n">
-        <v>0.75057</v>
+        <v>-0.75057</v>
       </c>
       <c r="N331" t="inlineStr">
         <is>
@@ -35130,16 +35150,16 @@
         </is>
       </c>
       <c r="I376" s="5" t="n">
-        <v>0.07467799999999999</v>
+        <v>-0.07467799999999999</v>
       </c>
       <c r="J376" s="5" t="n">
-        <v>0.059672</v>
+        <v>-0.059672</v>
       </c>
       <c r="K376" s="5" t="n">
-        <v>0.207794</v>
+        <v>-0.207794</v>
       </c>
       <c r="L376" s="5" t="n">
-        <v>0.039867</v>
+        <v>-0.039867</v>
       </c>
       <c r="M376" t="inlineStr">
         <is>
@@ -37159,13 +37179,13 @@
         </is>
       </c>
       <c r="F403" s="5" t="n">
-        <v>0.440706</v>
+        <v>-0.440706</v>
       </c>
       <c r="G403" s="5" t="n">
-        <v>3.736792</v>
+        <v>-3.736792</v>
       </c>
       <c r="H403" s="5" t="n">
-        <v>3.014239</v>
+        <v>-3.014239</v>
       </c>
       <c r="I403" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/AUXX.xlsx
+++ b/output/pdf_financials_xlsx/AUXX.xlsx
@@ -1959,19 +1959,19 @@
         <v>0.445559</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.030343</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.019771</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.162128</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.005882</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.005882</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>5.269421</v>
@@ -2045,19 +2045,19 @@
         <v>0.445559</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.030343</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.019771</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.162128</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.005882</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.005882</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>5.269421</v>
@@ -10108,7 +10108,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -11292,7 +11292,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -26704,7 +26704,7 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
@@ -31338,7 +31338,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
@@ -38228,7 +38228,7 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
